--- a/contest_entry_forms/018_halloween_restaurant_decoration_contest_form--contest_entry_forms.xlsx
+++ b/contest_entry_forms/018_halloween_restaurant_decoration_contest_form--contest_entry_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -937,7 +937,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>decoration_type_1</t>
+          <t>decoration type 1</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>decoration_type_2</t>
+          <t>decoration type 2</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>decoration_type_3</t>
+          <t>decoration type 3</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>decoration_image_1</t>
+          <t>decoration image 1</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>decoration_image_2</t>
+          <t>decoration image 2</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>decoration_image_3</t>
+          <t>decoration image 3</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>submission_status_1</t>
+          <t>submission status 1</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>submission_status_2</t>
+          <t>submission status 2</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>submission_status_3</t>
+          <t>submission status 3</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>submitted_by_1</t>
+          <t>submitted by 1</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>submitted_by_2</t>
+          <t>submitted by 2</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>submitted_by_3</t>
+          <t>submitted by 3</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>submitted_for_1</t>
+          <t>submitted for 1</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>submitted_for_2</t>
+          <t>submitted for 2</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>submitted_for_3</t>
+          <t>submitted for 3</t>
         </is>
       </c>
     </row>
